--- a/assets/data/capcollection.xlsx
+++ b/assets/data/capcollection.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Desktop\PROGRAMES\CapCollection\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Desktop\PROGRAMES\CapCollection\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F380443-F71E-4FCF-BA57-BCF2D69FE159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6F6DF2-8512-47E6-916D-B533F42FB189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="309">
   <si>
     <t>FONT D'OR</t>
   </si>
@@ -961,6 +961,18 @@
   </si>
   <si>
     <t>BITTER KAS</t>
+  </si>
+  <si>
+    <t>AQUARIUS (naranja) v2</t>
+  </si>
+  <si>
+    <t>image149.png</t>
+  </si>
+  <si>
+    <t>image150.png</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL (especial radler)</t>
   </si>
 </sst>
 </file>
@@ -6748,9 +6760,15 @@
       <c r="A150" s="1">
         <v>149</v>
       </c>
-      <c r="B150" s="4"/>
-      <c r="C150" s="4"/>
-      <c r="D150" s="5"/>
+      <c r="B150" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>306</v>
+      </c>
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
       <c r="G150" s="3"/>
@@ -6778,9 +6796,15 @@
       <c r="A151" s="1">
         <v>150</v>
       </c>
-      <c r="B151" s="4"/>
-      <c r="C151" s="4"/>
-      <c r="D151" s="5"/>
+      <c r="B151" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>307</v>
+      </c>
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
       <c r="G151" s="3"/>

--- a/assets/data/capcollection.xlsx
+++ b/assets/data/capcollection.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Desktop\PROGRAMES\CapCollection\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6F6DF2-8512-47E6-916D-B533F42FB189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7468C804-E851-45D3-9252-DB6042821224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="328">
   <si>
     <t>FONT D'OR</t>
   </si>
@@ -973,6 +973,63 @@
   </si>
   <si>
     <t>SAN MIGUEL (especial radler)</t>
+  </si>
+  <si>
+    <t>image151.png</t>
+  </si>
+  <si>
+    <t>image152.png</t>
+  </si>
+  <si>
+    <t>image153.png</t>
+  </si>
+  <si>
+    <t>image154.png</t>
+  </si>
+  <si>
+    <t>image155.png</t>
+  </si>
+  <si>
+    <t>image156.png</t>
+  </si>
+  <si>
+    <t>image157.png</t>
+  </si>
+  <si>
+    <t>image158.png</t>
+  </si>
+  <si>
+    <t>ICE PEAK (冰峰)</t>
+  </si>
+  <si>
+    <t>DAYAO (Li'ai)</t>
+  </si>
+  <si>
+    <t>B.R.O.T. (pet nat)</t>
+  </si>
+  <si>
+    <t>VINO</t>
+  </si>
+  <si>
+    <t>PEPSI</t>
+  </si>
+  <si>
+    <t>POWER STATION (动力火车)</t>
+  </si>
+  <si>
+    <t>COCKTAIL</t>
+  </si>
+  <si>
+    <t>GUANGMING (光明) BEER</t>
+  </si>
+  <si>
+    <t>BUDWEISER (fifa world cup 2026 edition)</t>
+  </si>
+  <si>
+    <t>unkown</t>
+  </si>
+  <si>
+    <t>unkown (奖)</t>
   </si>
 </sst>
 </file>
@@ -1064,7 +1121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1089,6 +1146,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1584,16 +1644,16 @@
     </row>
     <row r="6" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -1620,16 +1680,16 @@
     </row>
     <row r="7" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>104</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -1656,16 +1716,16 @@
     </row>
     <row r="8" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -1692,16 +1752,16 @@
     </row>
     <row r="9" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -1728,16 +1788,16 @@
     </row>
     <row r="10" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>124</v>
+        <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -1764,16 +1824,16 @@
     </row>
     <row r="11" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1800,16 +1860,16 @@
     </row>
     <row r="12" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -1836,16 +1896,16 @@
     </row>
     <row r="13" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1872,16 +1932,16 @@
     </row>
     <row r="14" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -1907,16 +1967,16 @@
     </row>
     <row r="15" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -1943,16 +2003,16 @@
     </row>
     <row r="16" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1979,16 +2039,16 @@
     </row>
     <row r="17" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -2015,16 +2075,16 @@
     </row>
     <row r="18" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -2051,16 +2111,16 @@
     </row>
     <row r="19" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -2087,16 +2147,16 @@
     </row>
     <row r="20" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -2123,16 +2183,16 @@
     </row>
     <row r="21" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>22</v>
+        <v>129</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>168</v>
+        <v>271</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -2158,16 +2218,16 @@
     </row>
     <row r="22" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>169</v>
+        <v>286</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -2194,16 +2254,16 @@
     </row>
     <row r="23" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>170</v>
+        <v>240</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -2230,16 +2290,16 @@
     </row>
     <row r="24" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>171</v>
+        <v>241</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -2266,16 +2326,16 @@
     </row>
     <row r="25" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>172</v>
+        <v>242</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -2302,16 +2362,16 @@
     </row>
     <row r="26" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>173</v>
+        <v>243</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -2338,16 +2398,16 @@
     </row>
     <row r="27" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>286</v>
+        <v>244</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -2374,16 +2434,16 @@
     </row>
     <row r="28" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>29</v>
+        <v>104</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>174</v>
+        <v>245</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -2410,16 +2470,16 @@
     </row>
     <row r="29" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>175</v>
+        <v>246</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -2446,16 +2506,16 @@
     </row>
     <row r="30" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>176</v>
+        <v>247</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -2482,16 +2542,16 @@
     </row>
     <row r="31" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>177</v>
+        <v>248</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -2518,16 +2578,16 @@
     </row>
     <row r="32" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>286</v>
+        <v>249</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -2554,16 +2614,16 @@
     </row>
     <row r="33" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -2590,16 +2650,16 @@
     </row>
     <row r="34" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>179</v>
+        <v>250</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -2626,16 +2686,16 @@
     </row>
     <row r="35" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>180</v>
+        <v>251</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -2662,16 +2722,16 @@
     </row>
     <row r="36" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>181</v>
+        <v>252</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -2698,16 +2758,16 @@
     </row>
     <row r="37" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -2734,16 +2794,16 @@
     </row>
     <row r="38" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>183</v>
+        <v>272</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -2770,16 +2830,16 @@
     </row>
     <row r="39" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -2806,16 +2866,16 @@
     </row>
     <row r="40" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>40</v>
+        <v>136</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>185</v>
+        <v>276</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -2842,16 +2902,16 @@
     </row>
     <row r="41" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>186</v>
+        <v>273</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -2878,16 +2938,16 @@
     </row>
     <row r="42" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -2914,16 +2974,16 @@
     </row>
     <row r="43" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>286</v>
+        <v>177</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -2950,16 +3010,16 @@
     </row>
     <row r="44" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>188</v>
+        <v>253</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -2986,16 +3046,16 @@
     </row>
     <row r="45" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -3022,16 +3082,16 @@
     </row>
     <row r="46" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>190</v>
+        <v>286</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -3058,16 +3118,16 @@
     </row>
     <row r="47" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -3094,16 +3154,16 @@
     </row>
     <row r="48" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
@@ -3130,16 +3190,16 @@
     </row>
     <row r="49" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D49" s="8" t="s">
-        <v>193</v>
+      <c r="D49" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -3166,16 +3226,16 @@
     </row>
     <row r="50" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -3202,16 +3262,16 @@
     </row>
     <row r="51" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -3238,16 +3298,16 @@
     </row>
     <row r="52" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -3274,16 +3334,16 @@
     </row>
     <row r="53" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -3310,16 +3370,16 @@
     </row>
     <row r="54" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
@@ -3346,16 +3406,16 @@
     </row>
     <row r="55" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>286</v>
+        <v>186</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
@@ -3382,16 +3442,16 @@
     </row>
     <row r="56" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
@@ -3418,16 +3478,16 @@
     </row>
     <row r="57" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>200</v>
+        <v>286</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
@@ -3454,16 +3514,16 @@
     </row>
     <row r="58" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
@@ -3490,16 +3550,16 @@
     </row>
     <row r="59" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>13</v>
+        <v>139</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>140</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>202</v>
+        <v>278</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
@@ -3526,16 +3586,16 @@
     </row>
     <row r="60" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>60</v>
+        <v>141</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>13</v>
+        <v>140</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>203</v>
+        <v>279</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
@@ -3562,16 +3622,16 @@
     </row>
     <row r="61" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>13</v>
+        <v>140</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>204</v>
+        <v>280</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
@@ -3598,16 +3658,16 @@
     </row>
     <row r="62" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>13</v>
+        <v>140</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>205</v>
+        <v>281</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
@@ -3634,16 +3694,16 @@
     </row>
     <row r="63" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
@@ -3670,16 +3730,16 @@
     </row>
     <row r="64" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
@@ -3706,16 +3766,16 @@
     </row>
     <row r="65" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
@@ -3742,16 +3802,16 @@
     </row>
     <row r="66" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
@@ -3778,16 +3838,16 @@
     </row>
     <row r="67" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
@@ -3814,16 +3874,16 @@
     </row>
     <row r="68" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D68" s="5" t="s">
-        <v>211</v>
+      <c r="D68" s="8" t="s">
+        <v>193</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
@@ -3849,16 +3909,16 @@
     </row>
     <row r="69" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
@@ -3884,16 +3944,16 @@
     </row>
     <row r="70" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
@@ -3920,16 +3980,16 @@
     </row>
     <row r="71" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
@@ -3956,16 +4016,16 @@
     </row>
     <row r="72" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>215</v>
+      <c r="D72" s="10" t="s">
+        <v>197</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
@@ -3992,16 +4052,16 @@
     </row>
     <row r="73" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>13</v>
+        <v>134</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>216</v>
+        <v>274</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
@@ -4027,16 +4087,16 @@
     </row>
     <row r="74" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>13</v>
+        <v>134</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
@@ -4063,16 +4123,16 @@
     </row>
     <row r="75" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
@@ -4099,16 +4159,16 @@
     </row>
     <row r="76" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>219</v>
+        <v>286</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
@@ -4135,16 +4195,16 @@
     </row>
     <row r="77" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
@@ -4171,16 +4231,16 @@
     </row>
     <row r="78" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
@@ -4207,16 +4267,16 @@
     </row>
     <row r="79" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
@@ -4243,16 +4303,16 @@
     </row>
     <row r="80" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
@@ -4279,16 +4339,16 @@
     </row>
     <row r="81" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
@@ -4315,16 +4375,16 @@
     </row>
     <row r="82" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
@@ -4351,16 +4411,16 @@
     </row>
     <row r="83" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
@@ -4387,16 +4447,16 @@
     </row>
     <row r="84" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
@@ -4423,16 +4483,16 @@
     </row>
     <row r="85" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
@@ -4459,16 +4519,16 @@
     </row>
     <row r="86" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
@@ -4495,16 +4555,16 @@
     </row>
     <row r="87" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
@@ -4531,16 +4591,16 @@
     </row>
     <row r="88" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
@@ -4567,16 +4627,16 @@
     </row>
     <row r="89" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
@@ -4603,16 +4663,16 @@
     </row>
     <row r="90" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
@@ -4639,16 +4699,16 @@
     </row>
     <row r="91" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
@@ -4675,16 +4735,16 @@
     </row>
     <row r="92" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
@@ -4711,16 +4771,16 @@
     </row>
     <row r="93" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
@@ -4747,16 +4807,16 @@
     </row>
     <row r="94" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
-        <v>136</v>
+        <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
@@ -4783,16 +4843,16 @@
     </row>
     <row r="95" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
@@ -4819,16 +4879,16 @@
     </row>
     <row r="96" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
@@ -4855,16 +4915,16 @@
     </row>
     <row r="97" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
@@ -4891,16 +4951,16 @@
     </row>
     <row r="98" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
@@ -4927,16 +4987,16 @@
     </row>
     <row r="99" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
@@ -4963,16 +5023,16 @@
     </row>
     <row r="100" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
@@ -4999,16 +5059,16 @@
     </row>
     <row r="101" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
@@ -5035,16 +5095,16 @@
     </row>
     <row r="102" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
@@ -5071,16 +5131,16 @@
     </row>
     <row r="103" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
@@ -5107,16 +5167,16 @@
     </row>
     <row r="104" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
@@ -5142,16 +5202,16 @@
     </row>
     <row r="105" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>107</v>
+        <v>6</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>248</v>
+        <v>154</v>
       </c>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
@@ -5177,16 +5237,16 @@
     </row>
     <row r="106" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>108</v>
+        <v>7</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>249</v>
+        <v>155</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
@@ -5212,16 +5272,16 @@
     </row>
     <row r="107" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
@@ -5248,16 +5308,16 @@
     </row>
     <row r="108" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>251</v>
+        <v>222</v>
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
@@ -5284,16 +5344,16 @@
     </row>
     <row r="109" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
@@ -5320,16 +5380,16 @@
     </row>
     <row r="110" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
@@ -5355,16 +5415,16 @@
     </row>
     <row r="111" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>113</v>
+        <v>8</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>254</v>
+        <v>156</v>
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
@@ -5391,16 +5451,16 @@
     </row>
     <row r="112" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>255</v>
+        <v>224</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
@@ -5427,16 +5487,16 @@
     </row>
     <row r="113" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
@@ -5463,16 +5523,16 @@
     </row>
     <row r="114" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
@@ -5499,16 +5559,16 @@
     </row>
     <row r="115" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
@@ -5535,16 +5595,16 @@
     </row>
     <row r="116" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
@@ -5571,16 +5631,16 @@
     </row>
     <row r="117" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
@@ -5607,16 +5667,16 @@
     </row>
     <row r="118" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
@@ -5643,16 +5703,16 @@
     </row>
     <row r="119" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>262</v>
+        <v>227</v>
       </c>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
@@ -5679,16 +5739,16 @@
     </row>
     <row r="120" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
@@ -5715,16 +5775,16 @@
     </row>
     <row r="121" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
@@ -5751,16 +5811,16 @@
     </row>
     <row r="122" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
@@ -5787,16 +5847,16 @@
     </row>
     <row r="123" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
@@ -5823,16 +5883,16 @@
     </row>
     <row r="124" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
@@ -5859,16 +5919,16 @@
     </row>
     <row r="125" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>268</v>
+        <v>157</v>
       </c>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
@@ -5895,16 +5955,16 @@
     </row>
     <row r="126" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
@@ -5931,16 +5991,16 @@
     </row>
     <row r="127" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
@@ -5967,16 +6027,16 @@
     </row>
     <row r="128" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>130</v>
+        <v>13</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>271</v>
+        <v>231</v>
       </c>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
@@ -6002,16 +6062,16 @@
     </row>
     <row r="129" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>130</v>
+        <v>13</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
@@ -6038,16 +6098,16 @@
     </row>
     <row r="130" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>130</v>
+        <v>13</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>273</v>
+        <v>233</v>
       </c>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
@@ -6074,16 +6134,16 @@
     </row>
     <row r="131" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>134</v>
+        <v>13</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>274</v>
+        <v>234</v>
       </c>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
@@ -6110,16 +6170,16 @@
     </row>
     <row r="132" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
@@ -6146,16 +6206,16 @@
     </row>
     <row r="133" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
-        <v>39</v>
+        <v>132</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
@@ -6182,16 +6242,16 @@
     </row>
     <row r="134" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
@@ -6218,16 +6278,16 @@
     </row>
     <row r="135" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C135" s="9" t="s">
-        <v>140</v>
+        <v>92</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>278</v>
+        <v>235</v>
       </c>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
@@ -6254,16 +6314,16 @@
     </row>
     <row r="136" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>140</v>
+        <v>13</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>279</v>
+        <v>236</v>
       </c>
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
@@ -6290,16 +6350,16 @@
     </row>
     <row r="137" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>140</v>
+        <v>13</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>280</v>
+        <v>237</v>
       </c>
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
@@ -6326,16 +6386,16 @@
     </row>
     <row r="138" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
-        <v>61</v>
+        <v>137</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
@@ -6362,16 +6422,16 @@
     </row>
     <row r="139" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>144</v>
+        <v>95</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>140</v>
+        <v>13</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
@@ -6828,13 +6888,19 @@
       <c r="Y151" s="3"/>
       <c r="Z151" s="3"/>
     </row>
-    <row r="152" spans="1:26" ht="13.75" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:26" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>151</v>
       </c>
-      <c r="B152" s="4"/>
-      <c r="C152" s="4"/>
-      <c r="D152" s="5"/>
+      <c r="B152" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>309</v>
+      </c>
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
       <c r="G152" s="3"/>
@@ -6858,13 +6924,19 @@
       <c r="Y152" s="3"/>
       <c r="Z152" s="3"/>
     </row>
-    <row r="153" spans="1:26" ht="13.75" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:26" ht="36.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>152</v>
       </c>
-      <c r="B153" s="4"/>
-      <c r="C153" s="4"/>
-      <c r="D153" s="5"/>
+      <c r="B153" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>310</v>
+      </c>
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
       <c r="G153" s="3"/>
@@ -6888,13 +6960,19 @@
       <c r="Y153" s="3"/>
       <c r="Z153" s="3"/>
     </row>
-    <row r="154" spans="1:26" ht="13.75" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:26" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>153</v>
       </c>
-      <c r="B154" s="4"/>
-      <c r="C154" s="4"/>
-      <c r="D154" s="5"/>
+      <c r="B154" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>311</v>
+      </c>
       <c r="E154" s="3"/>
       <c r="F154" s="3"/>
       <c r="G154" s="3"/>
@@ -6918,13 +6996,19 @@
       <c r="Y154" s="3"/>
       <c r="Z154" s="3"/>
     </row>
-    <row r="155" spans="1:26" ht="13.75" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:26" ht="42.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>154</v>
       </c>
-      <c r="B155" s="4"/>
-      <c r="C155" s="4"/>
-      <c r="D155" s="5"/>
+      <c r="B155" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>312</v>
+      </c>
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
       <c r="G155" s="3"/>
@@ -6948,13 +7032,19 @@
       <c r="Y155" s="3"/>
       <c r="Z155" s="3"/>
     </row>
-    <row r="156" spans="1:26" ht="13.75" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:26" ht="42.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>155</v>
       </c>
-      <c r="B156" s="4"/>
-      <c r="C156" s="4"/>
-      <c r="D156" s="5"/>
+      <c r="B156" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>313</v>
+      </c>
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
       <c r="G156" s="3"/>
@@ -6978,13 +7068,19 @@
       <c r="Y156" s="3"/>
       <c r="Z156" s="3"/>
     </row>
-    <row r="157" spans="1:26" ht="13.75" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:26" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>156</v>
       </c>
-      <c r="B157" s="4"/>
-      <c r="C157" s="4"/>
-      <c r="D157" s="5"/>
+      <c r="B157" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>314</v>
+      </c>
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
       <c r="G157" s="3"/>
@@ -7008,13 +7104,19 @@
       <c r="Y157" s="3"/>
       <c r="Z157" s="3"/>
     </row>
-    <row r="158" spans="1:26" ht="13.75" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:26" ht="36.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>157</v>
       </c>
-      <c r="B158" s="4"/>
-      <c r="C158" s="4"/>
-      <c r="D158" s="5"/>
+      <c r="B158" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>315</v>
+      </c>
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
       <c r="G158" s="3"/>
@@ -7038,13 +7140,19 @@
       <c r="Y158" s="3"/>
       <c r="Z158" s="3"/>
     </row>
-    <row r="159" spans="1:26" ht="13.75" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:26" ht="41.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>158</v>
       </c>
-      <c r="B159" s="4"/>
-      <c r="C159" s="4"/>
-      <c r="D159" s="5"/>
+      <c r="B159" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>316</v>
+      </c>
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
       <c r="G159" s="3"/>
@@ -30623,6 +30731,9 @@
       <c r="Z1000" s="3"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D162">
+    <sortCondition ref="A1:A162"/>
+  </sortState>
   <conditionalFormatting sqref="B2:C500">
     <cfRule type="expression" dxfId="9" priority="1">
       <formula>$C2="AGUA"</formula>

--- a/assets/data/capcollection.xlsx
+++ b/assets/data/capcollection.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Desktop\PROGRAMES\CapCollection\assets\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Desktop\PROGRAMES\BottleCapCollection\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7468C804-E851-45D3-9252-DB6042821224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3909D28D-88B3-4D81-ABE9-6B4550ACD354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="332">
   <si>
     <t>FONT D'OR</t>
   </si>
@@ -1030,6 +1030,18 @@
   </si>
   <si>
     <t>unkown (奖)</t>
+  </si>
+  <si>
+    <t>LA PROHIBIDA (cider)</t>
+  </si>
+  <si>
+    <t>image159.png</t>
+  </si>
+  <si>
+    <t>CIAO (bitter)</t>
+  </si>
+  <si>
+    <t>image160.png</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1146,9 +1158,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4024,7 +4033,7 @@
       <c r="C72" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D72" s="10" t="s">
+      <c r="D72" s="1" t="s">
         <v>197</v>
       </c>
       <c r="E72" s="3"/>
@@ -7176,13 +7185,19 @@
       <c r="Y159" s="3"/>
       <c r="Z159" s="3"/>
     </row>
-    <row r="160" spans="1:26" ht="13.75" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>159</v>
       </c>
-      <c r="B160" s="4"/>
-      <c r="C160" s="4"/>
-      <c r="D160" s="5"/>
+      <c r="B160" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D160" s="5" t="s">
+        <v>329</v>
+      </c>
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
       <c r="G160" s="3"/>
@@ -7206,13 +7221,19 @@
       <c r="Y160" s="3"/>
       <c r="Z160" s="3"/>
     </row>
-    <row r="161" spans="1:26" ht="13.75" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:26" ht="40.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>160</v>
       </c>
-      <c r="B161" s="4"/>
-      <c r="C161" s="4"/>
-      <c r="D161" s="5"/>
+      <c r="B161" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D161" s="5" t="s">
+        <v>331</v>
+      </c>
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
       <c r="G161" s="3"/>
@@ -7236,7 +7257,7 @@
       <c r="Y161" s="3"/>
       <c r="Z161" s="3"/>
     </row>
-    <row r="162" spans="1:26" ht="13.75" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>161</v>
       </c>

--- a/assets/data/capcollection.xlsx
+++ b/assets/data/capcollection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Desktop\PROGRAMES\BottleCapCollection\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3909D28D-88B3-4D81-ABE9-6B4550ACD354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9482355A-98D4-451F-BB6F-DE3241B86B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="338">
   <si>
     <t>FONT D'OR</t>
   </si>
@@ -445,10 +445,6 @@
     <t>KOPPARBERG (premium)</t>
   </si>
   <si>
-    <t>DESESPERADOS 
-(mojito, tequila flavoured)</t>
-  </si>
-  <si>
     <t>TEQUILA</t>
   </si>
   <si>
@@ -1042,13 +1038,35 @@
   </si>
   <si>
     <t>image160.png</t>
+  </si>
+  <si>
+    <t>DESPERADOS 
+(mojito, tequila flavoured)</t>
+  </si>
+  <si>
+    <t>image161.png</t>
+  </si>
+  <si>
+    <t>image162.png</t>
+  </si>
+  <si>
+    <t>image163.png</t>
+  </si>
+  <si>
+    <t>GALLO</t>
+  </si>
+  <si>
+    <t>GALLO (light)</t>
+  </si>
+  <si>
+    <t>SHANGRI-LA (by Dasani)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1085,6 +1103,14 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1106,7 +1132,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1129,11 +1155,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1156,15 +1197,275 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="40">
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FF7030A0"/>
+          <bgColor rgb="FFCC99FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB94F4F"/>
+          <bgColor rgb="FFB94F4F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF408BD0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC3A752"/>
+          <bgColor rgb="FFC3A752"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCCCCC"/>
+          <bgColor rgb="FFCCCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC391E3"/>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFE2F3"/>
+          <bgColor rgb="FFCFE2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FF7030A0"/>
+          <bgColor rgb="FFCC99FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB94F4F"/>
+          <bgColor rgb="FFB94F4F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF408BD0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC3A752"/>
+          <bgColor rgb="FFC3A752"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCCCCC"/>
+          <bgColor rgb="FFCCCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC391E3"/>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFE2F3"/>
+          <bgColor rgb="FFCFE2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FF7030A0"/>
+          <bgColor rgb="FFCC99FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB94F4F"/>
+          <bgColor rgb="FFB94F4F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF408BD0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC3A752"/>
+          <bgColor rgb="FFC3A752"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCCCCC"/>
+          <bgColor rgb="FFCCCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC391E3"/>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFE2F3"/>
+          <bgColor rgb="FFCFE2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1250,6 +1551,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCC99FF"/>
+      <color rgb="FF9966FF"/>
+      <color rgb="FF408BD0"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1463,27 +1771,27 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.61328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.69140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.765625" customWidth="1"/>
     <col min="2" max="2" width="37.3828125" customWidth="1"/>
     <col min="3" max="3" width="12.23046875" customWidth="1"/>
-    <col min="4" max="4" width="13.4609375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.23046875" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="13.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
@@ -1507,7 +1815,7 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1518,7 +1826,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -1543,7 +1851,7 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1554,7 +1862,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -1579,7 +1887,7 @@
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
     </row>
-    <row r="4" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1590,7 +1898,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -1615,7 +1923,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1626,7 +1934,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -1651,7 +1959,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1662,7 +1970,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -1687,7 +1995,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1698,7 +2006,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -1723,7 +2031,7 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
     </row>
-    <row r="8" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1734,7 +2042,7 @@
         <v>13</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -1759,7 +2067,7 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1770,7 +2078,7 @@
         <v>13</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -1795,7 +2103,7 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1806,7 +2114,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -1831,7 +2139,7 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1842,7 +2150,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1867,7 +2175,7 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
     </row>
-    <row r="12" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1878,7 +2186,7 @@
         <v>13</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -1903,7 +2211,7 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1914,7 +2222,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1939,7 +2247,7 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
     </row>
-    <row r="14" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1950,7 +2258,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -1974,7 +2282,7 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1985,7 +2293,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -2010,7 +2318,7 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
     </row>
-    <row r="16" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2021,7 +2329,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -2046,7 +2354,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2057,7 +2365,7 @@
         <v>13</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -2082,7 +2390,7 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2093,7 +2401,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -2118,7 +2426,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2129,7 +2437,7 @@
         <v>13</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -2154,7 +2462,7 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2165,7 +2473,7 @@
         <v>13</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -2190,7 +2498,7 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2201,7 +2509,7 @@
         <v>130</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -2225,7 +2533,7 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -2236,7 +2544,7 @@
         <v>13</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -2261,7 +2569,7 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -2272,7 +2580,7 @@
         <v>99</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -2297,7 +2605,7 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -2308,7 +2616,7 @@
         <v>99</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -2333,7 +2641,7 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -2344,7 +2652,7 @@
         <v>99</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -2369,7 +2677,7 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -2380,7 +2688,7 @@
         <v>99</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -2405,7 +2713,7 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
     </row>
-    <row r="27" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -2416,7 +2724,7 @@
         <v>99</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -2441,7 +2749,7 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
     </row>
-    <row r="28" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -2452,7 +2760,7 @@
         <v>99</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -2477,7 +2785,7 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -2488,7 +2796,7 @@
         <v>99</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -2513,7 +2821,7 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
     </row>
-    <row r="30" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -2524,7 +2832,7 @@
         <v>99</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -2549,7 +2857,7 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -2560,7 +2868,7 @@
         <v>99</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -2585,7 +2893,7 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -2596,7 +2904,7 @@
         <v>99</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -2621,7 +2929,7 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -2632,7 +2940,7 @@
         <v>11</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -2657,7 +2965,7 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
     </row>
-    <row r="34" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -2668,7 +2976,7 @@
         <v>99</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -2693,7 +3001,7 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -2704,7 +3012,7 @@
         <v>99</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -2729,7 +3037,7 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
     </row>
-    <row r="36" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -2740,7 +3048,7 @@
         <v>99</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -2765,7 +3073,7 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
     </row>
-    <row r="37" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -2776,7 +3084,7 @@
         <v>13</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -2801,7 +3109,7 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
     </row>
-    <row r="38" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -2812,7 +3120,7 @@
         <v>130</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -2837,7 +3145,7 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -2848,7 +3156,7 @@
         <v>13</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -2873,18 +3181,18 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
     </row>
-    <row r="40" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="D40" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -2909,7 +3217,7 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
     </row>
-    <row r="41" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -2920,7 +3228,7 @@
         <v>130</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -2945,7 +3253,7 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
     </row>
-    <row r="42" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -2956,7 +3264,7 @@
         <v>13</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -2981,7 +3289,7 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
     </row>
-    <row r="43" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -2992,7 +3300,7 @@
         <v>13</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -3017,7 +3325,7 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -3028,7 +3336,7 @@
         <v>99</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -3053,7 +3361,7 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
     </row>
-    <row r="45" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -3064,7 +3372,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -3089,7 +3397,7 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -3100,7 +3408,7 @@
         <v>13</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -3125,7 +3433,7 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
     </row>
-    <row r="47" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -3136,7 +3444,7 @@
         <v>13</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -3161,7 +3469,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -3172,7 +3480,7 @@
         <v>13</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
@@ -3197,7 +3505,7 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
     </row>
-    <row r="49" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -3208,7 +3516,7 @@
         <v>13</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -3233,7 +3541,7 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -3244,7 +3552,7 @@
         <v>13</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -3269,7 +3577,7 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
     </row>
-    <row r="51" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -3280,7 +3588,7 @@
         <v>13</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -3305,7 +3613,7 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -3316,7 +3624,7 @@
         <v>13</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -3341,7 +3649,7 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
     </row>
-    <row r="53" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -3352,7 +3660,7 @@
         <v>13</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -3377,7 +3685,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -3388,7 +3696,7 @@
         <v>13</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
@@ -3413,7 +3721,7 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
     </row>
-    <row r="55" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -3424,7 +3732,7 @@
         <v>13</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
@@ -3449,7 +3757,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -3460,7 +3768,7 @@
         <v>13</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
@@ -3485,7 +3793,7 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
     </row>
-    <row r="57" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -3496,7 +3804,7 @@
         <v>13</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
@@ -3521,7 +3829,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -3532,7 +3840,7 @@
         <v>13</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
@@ -3557,18 +3865,18 @@
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
     </row>
-    <row r="59" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C59" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C59" s="9" t="s">
-        <v>140</v>
-      </c>
       <c r="D59" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
@@ -3593,18 +3901,18 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
     </row>
-    <row r="60" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
@@ -3629,18 +3937,18 @@
       <c r="Y60" s="3"/>
       <c r="Z60" s="3"/>
     </row>
-    <row r="61" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
@@ -3665,18 +3973,18 @@
       <c r="Y61" s="3"/>
       <c r="Z61" s="3"/>
     </row>
-    <row r="62" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
@@ -3701,7 +4009,7 @@
       <c r="Y62" s="3"/>
       <c r="Z62" s="3"/>
     </row>
-    <row r="63" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -3712,7 +4020,7 @@
         <v>97</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
@@ -3737,7 +4045,7 @@
       <c r="Y63" s="3"/>
       <c r="Z63" s="3"/>
     </row>
-    <row r="64" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -3748,7 +4056,7 @@
         <v>13</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
@@ -3773,7 +4081,7 @@
       <c r="Y64" s="3"/>
       <c r="Z64" s="3"/>
     </row>
-    <row r="65" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -3784,7 +4092,7 @@
         <v>13</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
@@ -3809,7 +4117,7 @@
       <c r="Y65" s="3"/>
       <c r="Z65" s="3"/>
     </row>
-    <row r="66" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -3820,7 +4128,7 @@
         <v>13</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
@@ -3845,7 +4153,7 @@
       <c r="Y66" s="3"/>
       <c r="Z66" s="3"/>
     </row>
-    <row r="67" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -3856,7 +4164,7 @@
         <v>13</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
@@ -3881,7 +4189,7 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
     </row>
-    <row r="68" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -3891,8 +4199,8 @@
       <c r="C68" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D68" s="8" t="s">
-        <v>193</v>
+      <c r="D68" s="11" t="s">
+        <v>192</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
@@ -3916,7 +4224,7 @@
       <c r="Y68" s="3"/>
       <c r="Z68" s="3"/>
     </row>
-    <row r="69" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -3927,7 +4235,7 @@
         <v>13</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
@@ -3951,7 +4259,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="3"/>
     </row>
-    <row r="70" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -3962,7 +4270,7 @@
         <v>13</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
@@ -3987,7 +4295,7 @@
       <c r="Y70" s="3"/>
       <c r="Z70" s="3"/>
     </row>
-    <row r="71" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -3998,7 +4306,7 @@
         <v>13</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
@@ -4023,7 +4331,7 @@
       <c r="Y71" s="3"/>
       <c r="Z71" s="3"/>
     </row>
-    <row r="72" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -4033,8 +4341,8 @@
       <c r="C72" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>197</v>
+      <c r="D72" s="10" t="s">
+        <v>196</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
@@ -4059,18 +4367,18 @@
       <c r="Y72" s="3"/>
       <c r="Z72" s="3"/>
     </row>
-    <row r="73" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>72</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="C73" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>134</v>
-      </c>
       <c r="D73" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
@@ -4094,18 +4402,18 @@
       <c r="Y73" s="3"/>
       <c r="Z73" s="3"/>
     </row>
-    <row r="74" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
@@ -4130,7 +4438,7 @@
       <c r="Y74" s="3"/>
       <c r="Z74" s="3"/>
     </row>
-    <row r="75" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -4141,7 +4449,7 @@
         <v>13</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
@@ -4166,7 +4474,7 @@
       <c r="Y75" s="3"/>
       <c r="Z75" s="3"/>
     </row>
-    <row r="76" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -4177,7 +4485,7 @@
         <v>13</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
@@ -4202,7 +4510,7 @@
       <c r="Y76" s="3"/>
       <c r="Z76" s="3"/>
     </row>
-    <row r="77" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -4213,7 +4521,7 @@
         <v>13</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
@@ -4238,7 +4546,7 @@
       <c r="Y77" s="3"/>
       <c r="Z77" s="3"/>
     </row>
-    <row r="78" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -4249,7 +4557,7 @@
         <v>13</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
@@ -4274,7 +4582,7 @@
       <c r="Y78" s="3"/>
       <c r="Z78" s="3"/>
     </row>
-    <row r="79" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -4285,7 +4593,7 @@
         <v>13</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
@@ -4310,7 +4618,7 @@
       <c r="Y79" s="3"/>
       <c r="Z79" s="3"/>
     </row>
-    <row r="80" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -4321,7 +4629,7 @@
         <v>13</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
@@ -4346,7 +4654,7 @@
       <c r="Y80" s="3"/>
       <c r="Z80" s="3"/>
     </row>
-    <row r="81" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -4357,7 +4665,7 @@
         <v>13</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
@@ -4382,7 +4690,7 @@
       <c r="Y81" s="3"/>
       <c r="Z81" s="3"/>
     </row>
-    <row r="82" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -4393,7 +4701,7 @@
         <v>13</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
@@ -4418,7 +4726,7 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
     </row>
-    <row r="83" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -4429,7 +4737,7 @@
         <v>13</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
@@ -4454,7 +4762,7 @@
       <c r="Y83" s="3"/>
       <c r="Z83" s="3"/>
     </row>
-    <row r="84" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -4465,7 +4773,7 @@
         <v>13</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
@@ -4490,7 +4798,7 @@
       <c r="Y84" s="3"/>
       <c r="Z84" s="3"/>
     </row>
-    <row r="85" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -4501,7 +4809,7 @@
         <v>13</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
@@ -4526,7 +4834,7 @@
       <c r="Y85" s="3"/>
       <c r="Z85" s="3"/>
     </row>
-    <row r="86" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -4537,7 +4845,7 @@
         <v>13</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
@@ -4562,7 +4870,7 @@
       <c r="Y86" s="3"/>
       <c r="Z86" s="3"/>
     </row>
-    <row r="87" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -4573,7 +4881,7 @@
         <v>13</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
@@ -4598,7 +4906,7 @@
       <c r="Y87" s="3"/>
       <c r="Z87" s="3"/>
     </row>
-    <row r="88" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -4609,7 +4917,7 @@
         <v>13</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
@@ -4634,7 +4942,7 @@
       <c r="Y88" s="3"/>
       <c r="Z88" s="3"/>
     </row>
-    <row r="89" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -4645,7 +4953,7 @@
         <v>13</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
@@ -4670,7 +4978,7 @@
       <c r="Y89" s="3"/>
       <c r="Z89" s="3"/>
     </row>
-    <row r="90" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -4681,7 +4989,7 @@
         <v>13</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
@@ -4706,7 +5014,7 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
     </row>
-    <row r="91" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -4717,7 +5025,7 @@
         <v>13</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
@@ -4742,7 +5050,7 @@
       <c r="Y91" s="3"/>
       <c r="Z91" s="3"/>
     </row>
-    <row r="92" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -4753,7 +5061,7 @@
         <v>99</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
@@ -4778,7 +5086,7 @@
       <c r="Y92" s="3"/>
       <c r="Z92" s="3"/>
     </row>
-    <row r="93" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -4789,7 +5097,7 @@
         <v>13</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
@@ -4814,7 +5122,7 @@
       <c r="Y93" s="3"/>
       <c r="Z93" s="3"/>
     </row>
-    <row r="94" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -4825,7 +5133,7 @@
         <v>13</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
@@ -4850,7 +5158,7 @@
       <c r="Y94" s="3"/>
       <c r="Z94" s="3"/>
     </row>
-    <row r="95" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -4861,7 +5169,7 @@
         <v>13</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
@@ -4886,7 +5194,7 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
     </row>
-    <row r="96" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -4897,7 +5205,7 @@
         <v>13</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
@@ -4922,7 +5230,7 @@
       <c r="Y96" s="3"/>
       <c r="Z96" s="3"/>
     </row>
-    <row r="97" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -4933,7 +5241,7 @@
         <v>99</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
@@ -4958,7 +5266,7 @@
       <c r="Y97" s="3"/>
       <c r="Z97" s="3"/>
     </row>
-    <row r="98" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -4969,7 +5277,7 @@
         <v>13</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
@@ -4994,7 +5302,7 @@
       <c r="Y98" s="3"/>
       <c r="Z98" s="3"/>
     </row>
-    <row r="99" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -5005,7 +5313,7 @@
         <v>13</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
@@ -5030,7 +5338,7 @@
       <c r="Y99" s="3"/>
       <c r="Z99" s="3"/>
     </row>
-    <row r="100" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -5041,7 +5349,7 @@
         <v>13</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
@@ -5066,18 +5374,18 @@
       <c r="Y100" s="3"/>
       <c r="Z100" s="3"/>
     </row>
-    <row r="101" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
@@ -5102,7 +5410,7 @@
       <c r="Y101" s="3"/>
       <c r="Z101" s="3"/>
     </row>
-    <row r="102" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -5113,7 +5421,7 @@
         <v>99</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
@@ -5138,7 +5446,7 @@
       <c r="Y102" s="3"/>
       <c r="Z102" s="3"/>
     </row>
-    <row r="103" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -5149,7 +5457,7 @@
         <v>99</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
@@ -5174,7 +5482,7 @@
       <c r="Y103" s="3"/>
       <c r="Z103" s="3"/>
     </row>
-    <row r="104" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -5185,7 +5493,7 @@
         <v>13</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
@@ -5209,7 +5517,7 @@
       <c r="Y104" s="3"/>
       <c r="Z104" s="3"/>
     </row>
-    <row r="105" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -5220,7 +5528,7 @@
         <v>1</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
@@ -5244,7 +5552,7 @@
       <c r="Y105" s="3"/>
       <c r="Z105" s="3"/>
     </row>
-    <row r="106" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -5255,7 +5563,7 @@
         <v>1</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
@@ -5279,7 +5587,7 @@
       <c r="Y106" s="3"/>
       <c r="Z106" s="3"/>
     </row>
-    <row r="107" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -5290,7 +5598,7 @@
         <v>99</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
@@ -5315,7 +5623,7 @@
       <c r="Y107" s="3"/>
       <c r="Z107" s="3"/>
     </row>
-    <row r="108" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -5326,7 +5634,7 @@
         <v>13</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
@@ -5351,7 +5659,7 @@
       <c r="Y108" s="3"/>
       <c r="Z108" s="3"/>
     </row>
-    <row r="109" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -5362,7 +5670,7 @@
         <v>99</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
@@ -5387,7 +5695,7 @@
       <c r="Y109" s="3"/>
       <c r="Z109" s="3"/>
     </row>
-    <row r="110" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -5398,7 +5706,7 @@
         <v>13</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
@@ -5422,7 +5730,7 @@
       <c r="Y110" s="3"/>
       <c r="Z110" s="3"/>
     </row>
-    <row r="111" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -5433,7 +5741,7 @@
         <v>1</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
@@ -5458,7 +5766,7 @@
       <c r="Y111" s="3"/>
       <c r="Z111" s="3"/>
     </row>
-    <row r="112" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -5469,7 +5777,7 @@
         <v>13</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
@@ -5494,7 +5802,7 @@
       <c r="Y112" s="3"/>
       <c r="Z112" s="3"/>
     </row>
-    <row r="113" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -5505,7 +5813,7 @@
         <v>99</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
@@ -5530,7 +5838,7 @@
       <c r="Y113" s="3"/>
       <c r="Z113" s="3"/>
     </row>
-    <row r="114" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -5541,7 +5849,7 @@
         <v>13</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
@@ -5566,7 +5874,7 @@
       <c r="Y114" s="3"/>
       <c r="Z114" s="3"/>
     </row>
-    <row r="115" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -5577,7 +5885,7 @@
         <v>99</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
@@ -5602,7 +5910,7 @@
       <c r="Y115" s="3"/>
       <c r="Z115" s="3"/>
     </row>
-    <row r="116" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -5613,7 +5921,7 @@
         <v>99</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
@@ -5638,7 +5946,7 @@
       <c r="Y116" s="3"/>
       <c r="Z116" s="3"/>
     </row>
-    <row r="117" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -5649,7 +5957,7 @@
         <v>99</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
@@ -5674,7 +5982,7 @@
       <c r="Y117" s="3"/>
       <c r="Z117" s="3"/>
     </row>
-    <row r="118" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -5685,7 +5993,7 @@
         <v>13</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
@@ -5710,7 +6018,7 @@
       <c r="Y118" s="3"/>
       <c r="Z118" s="3"/>
     </row>
-    <row r="119" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -5721,7 +6029,7 @@
         <v>13</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
@@ -5746,7 +6054,7 @@
       <c r="Y119" s="3"/>
       <c r="Z119" s="3"/>
     </row>
-    <row r="120" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -5757,7 +6065,7 @@
         <v>13</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
@@ -5782,7 +6090,7 @@
       <c r="Y120" s="3"/>
       <c r="Z120" s="3"/>
     </row>
-    <row r="121" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -5793,7 +6101,7 @@
         <v>13</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
@@ -5818,7 +6126,7 @@
       <c r="Y121" s="3"/>
       <c r="Z121" s="3"/>
     </row>
-    <row r="122" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -5829,7 +6137,7 @@
         <v>99</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
@@ -5854,7 +6162,7 @@
       <c r="Y122" s="3"/>
       <c r="Z122" s="3"/>
     </row>
-    <row r="123" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -5865,7 +6173,7 @@
         <v>13</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
@@ -5890,7 +6198,7 @@
       <c r="Y123" s="3"/>
       <c r="Z123" s="3"/>
     </row>
-    <row r="124" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -5901,7 +6209,7 @@
         <v>99</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
@@ -5926,7 +6234,7 @@
       <c r="Y124" s="3"/>
       <c r="Z124" s="3"/>
     </row>
-    <row r="125" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -5937,7 +6245,7 @@
         <v>1</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
@@ -5962,7 +6270,7 @@
       <c r="Y125" s="3"/>
       <c r="Z125" s="3"/>
     </row>
-    <row r="126" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -5973,7 +6281,7 @@
         <v>99</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
@@ -5998,7 +6306,7 @@
       <c r="Y126" s="3"/>
       <c r="Z126" s="3"/>
     </row>
-    <row r="127" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -6009,7 +6317,7 @@
         <v>99</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
@@ -6034,7 +6342,7 @@
       <c r="Y127" s="3"/>
       <c r="Z127" s="3"/>
     </row>
-    <row r="128" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -6045,7 +6353,7 @@
         <v>13</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
@@ -6069,7 +6377,7 @@
       <c r="Y128" s="3"/>
       <c r="Z128" s="3"/>
     </row>
-    <row r="129" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -6080,7 +6388,7 @@
         <v>13</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
@@ -6105,7 +6413,7 @@
       <c r="Y129" s="3"/>
       <c r="Z129" s="3"/>
     </row>
-    <row r="130" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -6116,7 +6424,7 @@
         <v>13</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
@@ -6141,7 +6449,7 @@
       <c r="Y130" s="3"/>
       <c r="Z130" s="3"/>
     </row>
-    <row r="131" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -6152,7 +6460,7 @@
         <v>13</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
@@ -6177,7 +6485,7 @@
       <c r="Y131" s="3"/>
       <c r="Z131" s="3"/>
     </row>
-    <row r="132" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -6188,7 +6496,7 @@
         <v>99</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
@@ -6213,7 +6521,7 @@
       <c r="Y132" s="3"/>
       <c r="Z132" s="3"/>
     </row>
-    <row r="133" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -6224,7 +6532,7 @@
         <v>99</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
@@ -6249,7 +6557,7 @@
       <c r="Y133" s="3"/>
       <c r="Z133" s="3"/>
     </row>
-    <row r="134" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -6260,7 +6568,7 @@
         <v>99</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
@@ -6285,7 +6593,7 @@
       <c r="Y134" s="3"/>
       <c r="Z134" s="3"/>
     </row>
-    <row r="135" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -6296,7 +6604,7 @@
         <v>13</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
@@ -6321,7 +6629,7 @@
       <c r="Y135" s="3"/>
       <c r="Z135" s="3"/>
     </row>
-    <row r="136" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -6332,7 +6640,7 @@
         <v>13</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
@@ -6357,7 +6665,7 @@
       <c r="Y136" s="3"/>
       <c r="Z136" s="3"/>
     </row>
-    <row r="137" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -6368,7 +6676,7 @@
         <v>13</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
@@ -6393,18 +6701,18 @@
       <c r="Y137" s="3"/>
       <c r="Z137" s="3"/>
     </row>
-    <row r="138" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>137</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
@@ -6429,7 +6737,7 @@
       <c r="Y138" s="3"/>
       <c r="Z138" s="3"/>
     </row>
-    <row r="139" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -6440,7 +6748,7 @@
         <v>13</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
@@ -6465,18 +6773,18 @@
       <c r="Y139" s="3"/>
       <c r="Z139" s="3"/>
     </row>
-    <row r="140" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>139</v>
       </c>
       <c r="B140" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C140" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="C140" s="4" t="s">
+      <c r="D140" s="5" t="s">
         <v>284</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>285</v>
       </c>
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
@@ -6501,18 +6809,18 @@
       <c r="Y140" s="3"/>
       <c r="Z140" s="3"/>
     </row>
-    <row r="141" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>140</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
@@ -6537,18 +6845,18 @@
       <c r="Y141" s="3"/>
       <c r="Z141" s="3"/>
     </row>
-    <row r="142" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>141</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
@@ -6573,18 +6881,18 @@
       <c r="Y142" s="3"/>
       <c r="Z142" s="3"/>
     </row>
-    <row r="143" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>142</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
@@ -6609,18 +6917,18 @@
       <c r="Y143" s="3"/>
       <c r="Z143" s="3"/>
     </row>
-    <row r="144" spans="1:26" ht="40.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>143</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
@@ -6645,18 +6953,18 @@
       <c r="Y144" s="3"/>
       <c r="Z144" s="3"/>
     </row>
-    <row r="145" spans="1:26" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>144</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
@@ -6681,18 +6989,18 @@
       <c r="Y145" s="3"/>
       <c r="Z145" s="3"/>
     </row>
-    <row r="146" spans="1:26" ht="47.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>145</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
@@ -6717,18 +7025,18 @@
       <c r="Y146" s="3"/>
       <c r="Z146" s="3"/>
     </row>
-    <row r="147" spans="1:26" ht="48.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>146</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
@@ -6753,18 +7061,18 @@
       <c r="Y147" s="3"/>
       <c r="Z147" s="3"/>
     </row>
-    <row r="148" spans="1:26" ht="49.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>147</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
@@ -6789,18 +7097,18 @@
       <c r="Y148" s="3"/>
       <c r="Z148" s="3"/>
     </row>
-    <row r="149" spans="1:26" ht="46.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>148</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
@@ -6825,18 +7133,18 @@
       <c r="Y149" s="3"/>
       <c r="Z149" s="3"/>
     </row>
-    <row r="150" spans="1:26" ht="48.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>149</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
@@ -6861,18 +7169,18 @@
       <c r="Y150" s="3"/>
       <c r="Z150" s="3"/>
     </row>
-    <row r="151" spans="1:26" ht="47.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>150</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
@@ -6897,18 +7205,18 @@
       <c r="Y151" s="3"/>
       <c r="Z151" s="3"/>
     </row>
-    <row r="152" spans="1:26" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>151</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
@@ -6933,18 +7241,18 @@
       <c r="Y152" s="3"/>
       <c r="Z152" s="3"/>
     </row>
-    <row r="153" spans="1:26" ht="36.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>152</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
@@ -6969,21 +7277,21 @@
       <c r="Y153" s="3"/>
       <c r="Z153" s="3"/>
     </row>
-    <row r="154" spans="1:26" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>153</v>
       </c>
       <c r="B154" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C154" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="C154" s="4" t="s">
-        <v>320</v>
-      </c>
       <c r="D154" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E154" s="3"/>
-      <c r="F154" s="3"/>
+      <c r="F154" s="12"/>
       <c r="G154" s="3"/>
       <c r="H154" s="3"/>
       <c r="I154" s="3"/>
@@ -7005,18 +7313,18 @@
       <c r="Y154" s="3"/>
       <c r="Z154" s="3"/>
     </row>
-    <row r="155" spans="1:26" ht="42.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>154</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
@@ -7041,18 +7349,18 @@
       <c r="Y155" s="3"/>
       <c r="Z155" s="3"/>
     </row>
-    <row r="156" spans="1:26" ht="42.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>155</v>
       </c>
       <c r="B156" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C156" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="C156" s="4" t="s">
-        <v>323</v>
-      </c>
       <c r="D156" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
@@ -7077,18 +7385,18 @@
       <c r="Y156" s="3"/>
       <c r="Z156" s="3"/>
     </row>
-    <row r="157" spans="1:26" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>156</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
@@ -7113,18 +7421,18 @@
       <c r="Y157" s="3"/>
       <c r="Z157" s="3"/>
     </row>
-    <row r="158" spans="1:26" ht="36.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>157</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
@@ -7149,18 +7457,18 @@
       <c r="Y158" s="3"/>
       <c r="Z158" s="3"/>
     </row>
-    <row r="159" spans="1:26" ht="41.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>158</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
@@ -7185,18 +7493,18 @@
       <c r="Y159" s="3"/>
       <c r="Z159" s="3"/>
     </row>
-    <row r="160" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>159</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>130</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
@@ -7221,18 +7529,18 @@
       <c r="Y160" s="3"/>
       <c r="Z160" s="3"/>
     </row>
-    <row r="161" spans="1:26" ht="40.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>160</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
@@ -7261,9 +7569,15 @@
       <c r="A162" s="1">
         <v>161</v>
       </c>
-      <c r="B162" s="4"/>
-      <c r="C162" s="4"/>
-      <c r="D162" s="5"/>
+      <c r="B162" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>332</v>
+      </c>
       <c r="E162" s="3"/>
       <c r="F162" s="3"/>
       <c r="G162" s="3"/>
@@ -7287,11 +7601,19 @@
       <c r="Y162" s="3"/>
       <c r="Z162" s="3"/>
     </row>
-    <row r="163" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
-      <c r="A163" s="3"/>
-      <c r="B163" s="3"/>
-      <c r="C163" s="3"/>
-      <c r="D163" s="3"/>
+    <row r="163" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>333</v>
+      </c>
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
       <c r="G163" s="3"/>
@@ -7315,11 +7637,19 @@
       <c r="Y163" s="3"/>
       <c r="Z163" s="3"/>
     </row>
-    <row r="164" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
-      <c r="A164" s="3"/>
-      <c r="B164" s="3"/>
-      <c r="C164" s="3"/>
-      <c r="D164" s="3"/>
+    <row r="164" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>334</v>
+      </c>
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
       <c r="G164" s="3"/>
@@ -7343,8 +7673,8 @@
       <c r="Y164" s="3"/>
       <c r="Z164" s="3"/>
     </row>
-    <row r="165" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
-      <c r="A165" s="3"/>
+    <row r="165" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="1"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
@@ -7371,8 +7701,8 @@
       <c r="Y165" s="3"/>
       <c r="Z165" s="3"/>
     </row>
-    <row r="166" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
-      <c r="A166" s="3"/>
+    <row r="166" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="1"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
@@ -7399,8 +7729,8 @@
       <c r="Y166" s="3"/>
       <c r="Z166" s="3"/>
     </row>
-    <row r="167" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
-      <c r="A167" s="3"/>
+    <row r="167" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="1"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
@@ -7427,8 +7757,8 @@
       <c r="Y167" s="3"/>
       <c r="Z167" s="3"/>
     </row>
-    <row r="168" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
-      <c r="A168" s="3"/>
+    <row r="168" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="1"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
@@ -7455,8 +7785,8 @@
       <c r="Y168" s="3"/>
       <c r="Z168" s="3"/>
     </row>
-    <row r="169" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
-      <c r="A169" s="3"/>
+    <row r="169" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="1"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
@@ -7483,8 +7813,8 @@
       <c r="Y169" s="3"/>
       <c r="Z169" s="3"/>
     </row>
-    <row r="170" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
-      <c r="A170" s="3"/>
+    <row r="170" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="1"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
@@ -7511,7 +7841,7 @@
       <c r="Y170" s="3"/>
       <c r="Z170" s="3"/>
     </row>
-    <row r="171" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -7539,7 +7869,7 @@
       <c r="Y171" s="3"/>
       <c r="Z171" s="3"/>
     </row>
-    <row r="172" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -7567,7 +7897,7 @@
       <c r="Y172" s="3"/>
       <c r="Z172" s="3"/>
     </row>
-    <row r="173" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -7595,7 +7925,7 @@
       <c r="Y173" s="3"/>
       <c r="Z173" s="3"/>
     </row>
-    <row r="174" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -7623,7 +7953,7 @@
       <c r="Y174" s="3"/>
       <c r="Z174" s="3"/>
     </row>
-    <row r="175" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -30756,37 +31086,35 @@
     <sortCondition ref="A1:A162"/>
   </sortState>
   <conditionalFormatting sqref="B2:C500">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>$C2="AGUA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="18" priority="2">
       <formula>$C2="CERVEZA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="3">
+    <cfRule type="expression" dxfId="17" priority="3">
       <formula>$C2="REFRESCO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="16" priority="4">
       <formula>$C2="ZUMO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="15" priority="5">
       <formula>$C2="SIDRA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="14" priority="6">
       <formula>$C2="GASEOSA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="7">
+    <cfRule type="expression" dxfId="13" priority="7">
       <formula>$C2="BATIDO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="9">
+    <cfRule type="expression" dxfId="12" priority="8">
       <formula>$C2="VODKA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="10">
+    <cfRule type="expression" dxfId="11" priority="10">
       <formula>$C2="TEQUILA"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C102">
-    <cfRule type="notContainsBlanks" dxfId="0" priority="8">
-      <formula>LEN(TRIM(C102))&gt;0</formula>
+    <cfRule type="expression" dxfId="10" priority="11">
+      <formula>$C2="VINO"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/assets/data/capcollection.xlsx
+++ b/assets/data/capcollection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Desktop\PROGRAMES\BottleCapCollection\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9482355A-98D4-451F-BB6F-DE3241B86B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5892C04-5E98-4DBF-A7E0-A25BC83D657A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -134,14 +134,6 @@
     <t>WARSTEINER (premium beer)</t>
   </si>
   <si>
-    <t>DAMN VERDE 
- (August K. Damm 1876)</t>
-  </si>
-  <si>
-    <t>DAMN DORADA
- (August K. Damm 1876)</t>
-  </si>
-  <si>
     <t>TURIA MARZEN 
 (cervesa torrada 1935)</t>
   </si>
@@ -213,9 +205,6 @@
 (tournez pour ouvrir K)</t>
   </si>
   <si>
-    <t xml:space="preserve">CAMARO </t>
-  </si>
-  <si>
     <t>AMBAR (120)</t>
   </si>
   <si>
@@ -1060,13 +1049,24 @@
   </si>
   <si>
     <t>SHANGRI-LA (by Dasani)</t>
+  </si>
+  <si>
+    <t>DAMM VERDE 
+ (August K. Damm 1876)</t>
+  </si>
+  <si>
+    <t>DAMM DORADA
+ (August K. Damm 1876)</t>
+  </si>
+  <si>
+    <t>CAMARO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1105,6 +1105,13 @@
     </font>
     <font>
       <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -1174,7 +1181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1212,11 +1219,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill>
@@ -1273,255 +1283,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFC391E3"/>
           <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF2CC"/>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor rgb="FF7030A0"/>
-          <bgColor rgb="FFCC99FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB94F4F"/>
-          <bgColor rgb="FFB94F4F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF408BD0"/>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC3A752"/>
-          <bgColor rgb="FFC3A752"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCCCCC"/>
-          <bgColor rgb="FFCCCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC391E3"/>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF2CC"/>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor rgb="FF7030A0"/>
-          <bgColor rgb="FFCC99FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB94F4F"/>
-          <bgColor rgb="FFB94F4F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF408BD0"/>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC3A752"/>
-          <bgColor rgb="FFC3A752"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCCCCC"/>
-          <bgColor rgb="FFCCCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC391E3"/>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4CCCC"/>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF2CC"/>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCFE2F3"/>
-          <bgColor rgb="FFCFE2F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB94F4F"/>
-          <bgColor rgb="FFB94F4F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF26639A"/>
-          <bgColor rgb="FF26639A"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC3A752"/>
-          <bgColor rgb="FFC3A752"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCCCCC"/>
-          <bgColor rgb="FFCCCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC391E3"/>
-          <bgColor rgb="FFC391E3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1782,16 +1543,16 @@
   <sheetData>
     <row r="1" spans="1:26" ht="13.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
@@ -1826,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -1862,7 +1623,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -1898,7 +1659,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -1934,7 +1695,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -1970,7 +1731,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -2006,7 +1767,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -2042,7 +1803,7 @@
         <v>13</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -2078,7 +1839,7 @@
         <v>13</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -2114,7 +1875,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -2150,7 +1911,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -2186,7 +1947,7 @@
         <v>13</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -2222,7 +1983,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -2258,7 +2019,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -2293,7 +2054,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -2329,7 +2090,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -2365,7 +2126,7 @@
         <v>13</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -2401,7 +2162,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -2437,7 +2198,7 @@
         <v>13</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -2473,7 +2234,7 @@
         <v>13</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -2503,13 +2264,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -2544,7 +2305,7 @@
         <v>13</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -2574,13 +2335,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -2610,13 +2371,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -2646,13 +2407,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -2682,13 +2443,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -2718,13 +2479,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -2754,13 +2515,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -2790,13 +2551,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -2826,13 +2587,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -2862,13 +2623,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -2898,13 +2659,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -2940,7 +2701,7 @@
         <v>11</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -2970,13 +2731,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -3006,13 +2767,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -3042,13 +2803,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -3084,7 +2845,7 @@
         <v>13</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -3114,13 +2875,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -3156,7 +2917,7 @@
         <v>13</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -3186,13 +2947,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -3222,13 +2983,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -3264,7 +3025,7 @@
         <v>13</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -3300,7 +3061,7 @@
         <v>13</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -3330,13 +3091,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -3372,7 +3133,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -3408,7 +3169,7 @@
         <v>13</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -3444,7 +3205,7 @@
         <v>13</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -3480,7 +3241,7 @@
         <v>13</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
@@ -3516,7 +3277,7 @@
         <v>13</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -3545,14 +3306,14 @@
       <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>36</v>
+      <c r="B50" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -3581,19 +3342,19 @@
       <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>37</v>
+      <c r="B51" s="9" t="s">
+        <v>336</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
+      <c r="H51" s="13"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
@@ -3618,13 +3379,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -3654,13 +3415,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -3690,13 +3451,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
@@ -3726,13 +3487,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
@@ -3762,13 +3523,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
@@ -3798,13 +3559,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
@@ -3834,13 +3595,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
@@ -3870,13 +3631,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
@@ -3906,13 +3667,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
@@ -3942,13 +3703,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
@@ -3978,13 +3739,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
@@ -4014,13 +3775,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
@@ -4050,13 +3811,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
@@ -4086,13 +3847,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
@@ -4122,13 +3883,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
@@ -4158,13 +3919,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
@@ -4194,13 +3955,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
@@ -4229,13 +3990,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
@@ -4264,13 +4025,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
@@ -4300,13 +4061,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
@@ -4336,13 +4097,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
@@ -4372,13 +4133,13 @@
         <v>72</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
@@ -4407,13 +4168,13 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
@@ -4443,13 +4204,13 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
@@ -4479,13 +4240,13 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
@@ -4515,13 +4276,13 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
@@ -4551,13 +4312,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
@@ -4587,13 +4348,13 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
@@ -4623,13 +4384,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>59</v>
+        <v>337</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
@@ -4659,13 +4420,13 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
@@ -4695,13 +4456,13 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
@@ -4731,13 +4492,13 @@
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
@@ -4767,13 +4528,13 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
@@ -4803,13 +4564,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
@@ -4839,13 +4600,13 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
@@ -4875,13 +4636,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
@@ -4911,13 +4672,13 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
@@ -4947,13 +4708,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
@@ -4983,13 +4744,13 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
@@ -5019,13 +4780,13 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
@@ -5055,13 +4816,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
@@ -5091,13 +4852,13 @@
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
@@ -5127,13 +4888,13 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
@@ -5163,13 +4924,13 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
@@ -5199,13 +4960,13 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
@@ -5235,13 +4996,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
@@ -5271,13 +5032,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
@@ -5307,13 +5068,13 @@
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
@@ -5343,13 +5104,13 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
@@ -5379,13 +5140,13 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
@@ -5415,13 +5176,13 @@
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
@@ -5451,13 +5212,13 @@
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
@@ -5487,13 +5248,13 @@
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
@@ -5528,7 +5289,7 @@
         <v>1</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
@@ -5563,7 +5324,7 @@
         <v>1</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
@@ -5592,13 +5353,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
@@ -5628,13 +5389,13 @@
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
@@ -5664,13 +5425,13 @@
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
@@ -5700,13 +5461,13 @@
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
@@ -5741,7 +5502,7 @@
         <v>1</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
@@ -5771,13 +5532,13 @@
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
@@ -5807,13 +5568,13 @@
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
@@ -5843,13 +5604,13 @@
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
@@ -5879,13 +5640,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
@@ -5915,13 +5676,13 @@
         <v>115</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
@@ -5951,13 +5712,13 @@
         <v>116</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
@@ -5987,13 +5748,13 @@
         <v>117</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
@@ -6023,13 +5784,13 @@
         <v>118</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
@@ -6059,13 +5820,13 @@
         <v>119</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
@@ -6095,13 +5856,13 @@
         <v>120</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
@@ -6131,13 +5892,13 @@
         <v>121</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
@@ -6167,13 +5928,13 @@
         <v>122</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
@@ -6203,13 +5964,13 @@
         <v>123</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
@@ -6245,7 +6006,7 @@
         <v>1</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
@@ -6275,13 +6036,13 @@
         <v>125</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
@@ -6311,13 +6072,13 @@
         <v>126</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
@@ -6347,13 +6108,13 @@
         <v>127</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
@@ -6382,13 +6143,13 @@
         <v>128</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
@@ -6418,13 +6179,13 @@
         <v>129</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
@@ -6454,13 +6215,13 @@
         <v>130</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
@@ -6490,13 +6251,13 @@
         <v>131</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
@@ -6526,13 +6287,13 @@
         <v>132</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
@@ -6562,13 +6323,13 @@
         <v>133</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
@@ -6598,13 +6359,13 @@
         <v>134</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
@@ -6634,13 +6395,13 @@
         <v>135</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
@@ -6670,13 +6431,13 @@
         <v>136</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
@@ -6706,13 +6467,13 @@
         <v>137</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
@@ -6742,13 +6503,13 @@
         <v>138</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
@@ -6778,13 +6539,13 @@
         <v>139</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
@@ -6814,13 +6575,13 @@
         <v>140</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
@@ -6850,13 +6611,13 @@
         <v>141</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
@@ -6886,13 +6647,13 @@
         <v>142</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
@@ -6922,13 +6683,13 @@
         <v>143</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
@@ -6958,13 +6719,13 @@
         <v>144</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
@@ -6994,13 +6755,13 @@
         <v>145</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
@@ -7030,13 +6791,13 @@
         <v>146</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
@@ -7066,13 +6827,13 @@
         <v>147</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
@@ -7102,13 +6863,13 @@
         <v>148</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
@@ -7138,13 +6899,13 @@
         <v>149</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
@@ -7174,13 +6935,13 @@
         <v>150</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
@@ -7210,13 +6971,13 @@
         <v>151</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
@@ -7246,13 +7007,13 @@
         <v>152</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
@@ -7282,13 +7043,13 @@
         <v>153</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E154" s="3"/>
       <c r="F154" s="12"/>
@@ -7318,13 +7079,13 @@
         <v>154</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
@@ -7354,13 +7115,13 @@
         <v>155</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
@@ -7390,13 +7151,13 @@
         <v>156</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
@@ -7426,13 +7187,13 @@
         <v>157</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
@@ -7462,13 +7223,13 @@
         <v>158</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
@@ -7498,13 +7259,13 @@
         <v>159</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
@@ -7534,13 +7295,13 @@
         <v>160</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
@@ -7570,13 +7331,13 @@
         <v>161</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E162" s="3"/>
       <c r="F162" s="3"/>
@@ -7606,13 +7367,13 @@
         <v>162</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
@@ -7642,13 +7403,13 @@
         <v>163</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
@@ -31086,34 +30847,34 @@
     <sortCondition ref="A1:A162"/>
   </sortState>
   <conditionalFormatting sqref="B2:C500">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>$C2="AGUA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>$C2="CERVEZA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="3">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>$C2="REFRESCO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>$C2="ZUMO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>$C2="SIDRA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="6">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>$C2="GASEOSA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="7">
+    <cfRule type="expression" dxfId="3" priority="7">
       <formula>$C2="BATIDO"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="8">
+    <cfRule type="expression" dxfId="2" priority="8">
       <formula>$C2="VODKA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="10">
+    <cfRule type="expression" dxfId="1" priority="10">
       <formula>$C2="TEQUILA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>$C2="VINO"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/assets/data/capcollection.xlsx
+++ b/assets/data/capcollection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Desktop\PROGRAMES\BottleCapCollection\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5892C04-5E98-4DBF-A7E0-A25BC83D657A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7908AC-9DF2-4903-B5EF-6B3215BF267E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="337">
   <si>
     <t>FONT D'OR</t>
   </si>
@@ -1011,12 +1011,6 @@
     <t>BUDWEISER (fifa world cup 2026 edition)</t>
   </si>
   <si>
-    <t>unkown</t>
-  </si>
-  <si>
-    <t>unkown (奖)</t>
-  </si>
-  <si>
     <t>LA PROHIBIDA (cider)</t>
   </si>
   <si>
@@ -1060,6 +1054,9 @@
   </si>
   <si>
     <t>CAMARO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DAYAO (奖)</t>
   </si>
 </sst>
 </file>
@@ -3307,7 +3304,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>13</v>
@@ -3343,7 +3340,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>13</v>
@@ -4133,7 +4130,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>130</v>
@@ -4384,7 +4381,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>13</v>
@@ -7223,10 +7220,10 @@
         <v>158</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>322</v>
+        <v>96</v>
       </c>
       <c r="D159" s="5" t="s">
         <v>312</v>
@@ -7259,13 +7256,13 @@
         <v>159</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>127</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
@@ -7295,13 +7292,13 @@
         <v>160</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>96</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
@@ -7331,13 +7328,13 @@
         <v>161</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E162" s="3"/>
       <c r="F162" s="3"/>
@@ -7367,13 +7364,13 @@
         <v>162</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
@@ -7403,13 +7400,13 @@
         <v>163</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>

--- a/assets/data/capcollection.xlsx
+++ b/assets/data/capcollection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Desktop\PROGRAMES\BottleCapCollection\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7908AC-9DF2-4903-B5EF-6B3215BF267E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C6C669-D16E-4B59-AAD2-AC5EE9C7B5D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1056,7 +1056,7 @@
     <t>CAMARO</t>
   </si>
   <si>
-    <t xml:space="preserve"> DAYAO (奖)</t>
+    <t>DAYAO (奖)</t>
   </si>
 </sst>
 </file>
